--- a/artfynd/A 69709-2021 artfynd.xlsx
+++ b/artfynd/A 69709-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 69709-2021 artfynd.xlsx
+++ b/artfynd/A 69709-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>112337924</v>
       </c>
       <c r="B2" t="n">
-        <v>90898</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93223</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -806,6 +801,129 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>107558915</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57141</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Tjäder, Brattfallet, Vrm</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>415857</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6686292</v>
+      </c>
+      <c r="S3" t="n">
+        <v>25</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-03-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>19:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Jonas Göransson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Jonas Göransson, Magnus Malmqvist, Erik Löfroth, Shoko Sato, Daniel Hertz Wallin , Jenny NILSSON, Olavi Niemelä, Kim Ohlsson</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Uggleinventering Klarälvdalens folkhögskola</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 69709-2021 artfynd.xlsx
+++ b/artfynd/A 69709-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -801,6 +806,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337924</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,8 +934,17 @@
           <t>Uggleinventering Klarälvdalens folkhögskola</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107558915</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>